--- a/tests/fixtures/sipri/milex_workbook_synthetic.xlsx
+++ b/tests/fixtures/sipri/milex_workbook_synthetic.xlsx
@@ -2526,7 +2526,7 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>1.5</v>
+        <v>0.15</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
